--- a/src/pandorafits/formats/nirda/level0-headers.xlsx
+++ b/src/pandorafits/formats/nirda/level0-headers.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/fileformats/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/nirda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B02444-FEFA-B145-933C-DE6026E9EB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338D6B85-CABB-7147-8EC4-4F6938B369F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17060" activeTab="1" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
+    <workbookView xWindow="-51200" yWindow="-9160" windowWidth="23100" windowHeight="28800" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
   </bookViews>
   <sheets>
-    <sheet name="Primary" sheetId="1" r:id="rId1"/>
+    <sheet name="Primary" sheetId="3" r:id="rId1"/>
     <sheet name="Ext0" sheetId="2" r:id="rId2"/>
+    <sheet name="Primary Old" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="195">
   <si>
     <t>SIMPLE</t>
   </si>
@@ -313,13 +314,322 @@
   </si>
   <si>
     <t>NASA Pandora</t>
+  </si>
+  <si>
+    <t>Compression type used for transmission of image data</t>
+  </si>
+  <si>
+    <t>SIDECAR Temperature at start of integration</t>
+  </si>
+  <si>
+    <t>CCE Compressor Reject Temperature at start of integration</t>
+  </si>
+  <si>
+    <t>CCE Cold Tip1 Temperature at start of integration</t>
+  </si>
+  <si>
+    <t>CCE Cold Tip2 Temperature at start of integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMPLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAXIS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTEND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTNAME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEXTEND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMDATA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCIDATA </t>
+  </si>
+  <si>
+    <t>CAMERAID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREATOR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRSOFTV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICEX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICEY </t>
+  </si>
+  <si>
+    <t>COMPTYPE</t>
+  </si>
+  <si>
+    <t>TRANSID</t>
+  </si>
+  <si>
+    <t>FILENAME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BINSIZE </t>
+  </si>
+  <si>
+    <t>BITDEPTH</t>
+  </si>
+  <si>
+    <t>BITSPIX</t>
+  </si>
+  <si>
+    <t>ROISIZEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMAND </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIG1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIG2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIG3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAINREG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESETS1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESETS2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DROPS1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DROPS2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DROPS3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">READS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROUPS </t>
+  </si>
+  <si>
+    <t>INTEGRTS</t>
+  </si>
+  <si>
+    <t>EXPOSRES</t>
+  </si>
+  <si>
+    <t>ENDDELAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSTSINC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRPSINC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRMSTOT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRMSEXP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRMSACQ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRMTIME </t>
+  </si>
+  <si>
+    <t>TSIDECAR</t>
+  </si>
+  <si>
+    <t>TCOMPRJT</t>
+  </si>
+  <si>
+    <t>TCLDTIP1</t>
+  </si>
+  <si>
+    <t>TCLDTIP2</t>
+  </si>
+  <si>
+    <t>Pandora MOC</t>
+  </si>
+  <si>
+    <t>Conforms to FITS standard</t>
+  </si>
+  <si>
+    <t>Number of dimensions</t>
+  </si>
+  <si>
+    <t>File contains extensions</t>
+  </si>
+  <si>
+    <t>Name of extension</t>
+  </si>
+  <si>
+    <t>Number of standard extensions</t>
+  </si>
+  <si>
+    <t>Simulated data</t>
+  </si>
+  <si>
+    <t>Science data</t>
+  </si>
+  <si>
+    <t>Telescope</t>
+  </si>
+  <si>
+    <t>ID of camera used in acquisition.</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>Creator of this product</t>
+  </si>
+  <si>
+    <t>Flight software version used to generate data</t>
+  </si>
+  <si>
+    <t>TransactionID for data packet</t>
+  </si>
+  <si>
+    <t>Path to file on payload OS.</t>
+  </si>
+  <si>
+    <t>Number of pixels N used to bin NxN-&gt;1</t>
+  </si>
+  <si>
+    <t>Effective bit depth in image</t>
+  </si>
+  <si>
+    <t>Bit depth of camera in acquisition</t>
+  </si>
+  <si>
+    <t>ROI Start X used in exposures</t>
+  </si>
+  <si>
+    <t>ROI Start Y used in exposures</t>
+  </si>
+  <si>
+    <t>ROI Start Z used in exposures</t>
+  </si>
+  <si>
+    <t>ROI Size X used in exposures</t>
+  </si>
+  <si>
+    <t>ROI Size Y used in exposures</t>
+  </si>
+  <si>
+    <t>ROI Size Z used in exposures</t>
+  </si>
+  <si>
+    <t>Bit noise parameter for Rice compression</t>
+  </si>
+  <si>
+    <t>Maximum prefix value for Rice compression</t>
+  </si>
+  <si>
+    <t>Seconds since the TAI Epoch</t>
+  </si>
+  <si>
+    <t>Nanoseconds added to CORSTIME]</t>
+  </si>
+  <si>
+    <t>SIDECAR command that generated data</t>
+  </si>
+  <si>
+    <t>SC_Config1 value in acquire</t>
+  </si>
+  <si>
+    <t>SC_Config2 value in acquire</t>
+  </si>
+  <si>
+    <t>SC_Config3 value in acquire</t>
+  </si>
+  <si>
+    <t>SC_GainVal value in acquire</t>
+  </si>
+  <si>
+    <t>SC_Resets1 value in acquire</t>
+  </si>
+  <si>
+    <t>SC_Resets2 value in acquire</t>
+  </si>
+  <si>
+    <t>SC_DropFrames1 value in acquire</t>
+  </si>
+  <si>
+    <t>SC_DropFrames2 value in acquire</t>
+  </si>
+  <si>
+    <t>SC_DropFrames3 value in acquire</t>
+  </si>
+  <si>
+    <t>SC_ReadFrames value for acquire</t>
+  </si>
+  <si>
+    <t>SC_Groups value for acquire</t>
+  </si>
+  <si>
+    <t>SC_Integrations value for acquire</t>
+  </si>
+  <si>
+    <t>SC_Exposures value for acquire</t>
+  </si>
+  <si>
+    <t>SC_EndDelay value for acquire</t>
+  </si>
+  <si>
+    <t>Reset frames included in datacube?</t>
+  </si>
+  <si>
+    <t>Drop frames included in datacube?</t>
+  </si>
+  <si>
+    <t>Total #frames clocked in acquire</t>
+  </si>
+  <si>
+    <t>#frames expected to be acquired from MACIE/SIDECAR</t>
+  </si>
+  <si>
+    <t>#frames actually acquired from + MACIE/SIDECAR</t>
+  </si>
+  <si>
+    <t>Frame time in ms</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>H2rgCam</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -333,6 +643,18 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFA31515"/>
+      <name val="Menlo"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -355,9 +677,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -691,12 +1016,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81127257-918B-0849-8077-19480435CD41}">
-  <dimension ref="A1:C36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC39856-FEAC-2E4C-B2DC-FF54B699906E}">
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="45.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -711,304 +1035,460 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="b">
-        <v>1</v>
+      <c r="A2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s">
+        <v>190</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>8</v>
+      <c r="A3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>191</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
+      <c r="A4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" t="s">
+        <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>5</v>
+      <c r="A5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>6</v>
+      <c r="A6" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
+      <c r="A7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>193</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>8</v>
+      <c r="A8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" t="s">
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>9</v>
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>91</v>
+      <c r="A10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>12</v>
+      <c r="A12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" t="s">
+        <v>141</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>13</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>14</v>
+      <c r="A14" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>15</v>
+      <c r="A15" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>16</v>
+      <c r="A16" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>17</v>
+      <c r="A17" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>18</v>
+      <c r="A18" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>19</v>
+      <c r="A19" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="C23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>25</v>
+      <c r="A25" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>26</v>
+      <c r="A26" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>27</v>
+      <c r="A27" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>28</v>
+      <c r="A28" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>29</v>
+      <c r="A29" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>30</v>
+      <c r="A30" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>31</v>
+      <c r="A31" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>32</v>
+      <c r="A32" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>33</v>
+      <c r="A33" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>34</v>
+      <c r="A34" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>35</v>
+      <c r="A35" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>36</v>
+      <c r="A36" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C43" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C47" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C48" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C49" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C51" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C53" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1141,4 +1621,330 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81127257-918B-0849-8077-19480435CD41}">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="39.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>